--- a/erp-server/erp-server-file/src/main/resources/excel/wms/warehouseLocation.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/warehouseLocation.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="导出" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,99 +27,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>所属仓库</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>所属</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>库区</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>仓位编码</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>仓位名称</t>
-    </r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>仓位编码</t>
+  </si>
+  <si>
+    <t>仓位名称</t>
+  </si>
+  <si>
+    <t>所属仓库</t>
+  </si>
+  <si>
+    <t>所属库区</t>
+  </si>
+  <si>
+    <t>仓位状态</t>
+  </si>
+  <si>
+    <t>启用状态</t>
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>更新人</t>
+  </si>
+  <si>
+    <t>更新时间</t>
+  </si>
+  <si>
+    <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.name}</t>
+  </si>
+  <si>
+    <t>{.warehouseName}</t>
+  </si>
+  <si>
+    <t>{.warehouseAreaName}</t>
+  </si>
+  <si>
+    <t>{.status}</t>
+  </si>
+  <si>
+    <t>{.disabled}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.updateUserName}</t>
+  </si>
+  <si>
+    <t>{.updateTime}</t>
   </si>
 </sst>
 </file>
@@ -137,14 +96,20 @@
   <fonts count="22">
     <font>
       <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -293,14 +258,8 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -309,6 +268,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -494,12 +459,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -602,73 +582,70 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,82 +660,85 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -812,7 +792,221 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -822,9 +1016,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -838,31 +1032,31 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
@@ -934,40 +1128,66 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -981,38 +1201,20 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
@@ -1071,17 +1273,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="12.875" customWidth="1"/>
-    <col min="3" max="3" width="11.625" customWidth="1"/>
-    <col min="4" max="4" width="12.375" customWidth="1"/>
-    <col min="5" max="5" width="23.125" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="70" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:5">
+    <row r="1" ht="15" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1094,37 +1299,53 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>